--- a/BD.xlsx
+++ b/BD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\barevalo\OneDrive - Tecnológica de Alimentos S.A\Balois -2024\GITHUB CP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tasaomega-my.sharepoint.com/personal/barevalo_tasa_com_pe1/Documents/Balois -2024/GITHUB CP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34CBA43-F557-4DB6-BA1B-498EE36F12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{E34CBA43-F557-4DB6-BA1B-498EE36F12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28631E61-86CE-47FD-B7EC-F50189A11382}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026-2" sheetId="16" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="361">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1098,6 +1098,33 @@
   </si>
   <si>
     <t>EP SIMY 3</t>
+  </si>
+  <si>
+    <t>REM DEXTER ( EX D DOG)</t>
+  </si>
+  <si>
+    <t>A.S/0066</t>
+  </si>
+  <si>
+    <t>A.S/0066-226</t>
+  </si>
+  <si>
+    <t>EP TASA 218</t>
+  </si>
+  <si>
+    <t>G.P/0002</t>
+  </si>
+  <si>
+    <t>G.P/0002-226</t>
+  </si>
+  <si>
+    <t>EP TASA 210</t>
+  </si>
+  <si>
+    <t>G.P/0001</t>
+  </si>
+  <si>
+    <t>G.P/0001-226</t>
   </si>
 </sst>
 </file>
@@ -1531,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406CE352-F3DC-4CF5-AA00-B0ED30D6C318}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
@@ -1699,10 +1726,55 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C10" s="1"/>
+      <c r="A10" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" t="s">
+        <v>353</v>
+      </c>
+      <c r="E10" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C11" s="1"/>
+      <c r="A11" t="s">
+        <v>331</v>
+      </c>
+      <c r="B11" t="s">
+        <v>355</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" t="s">
+        <v>356</v>
+      </c>
+      <c r="E11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>331</v>
+      </c>
+      <c r="B12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" t="s">
+        <v>359</v>
+      </c>
+      <c r="E12" t="s">
+        <v>360</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
